--- a/data/nzd0146/nzd0146.xlsx
+++ b/data/nzd0146/nzd0146.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I658"/>
+  <dimension ref="A1:I662"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22126,6 +22126,138 @@
         <v>360.19</v>
       </c>
       <c r="I658" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="659">
+      <c r="A659" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-03 22:11:19+00:00</t>
+        </is>
+      </c>
+      <c r="B659" t="n">
+        <v>371.37</v>
+      </c>
+      <c r="C659" t="n">
+        <v>371.18</v>
+      </c>
+      <c r="D659" t="n">
+        <v>370.18</v>
+      </c>
+      <c r="E659" t="n">
+        <v>369.46</v>
+      </c>
+      <c r="F659" t="n">
+        <v>368.1</v>
+      </c>
+      <c r="G659" t="n">
+        <v>360.33</v>
+      </c>
+      <c r="H659" t="n">
+        <v>360.42</v>
+      </c>
+      <c r="I659" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="660">
+      <c r="A660" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-11 22:11:13+00:00</t>
+        </is>
+      </c>
+      <c r="B660" t="n">
+        <v>371.21</v>
+      </c>
+      <c r="C660" t="n">
+        <v>370.31</v>
+      </c>
+      <c r="D660" t="n">
+        <v>368.6</v>
+      </c>
+      <c r="E660" t="n">
+        <v>367.77</v>
+      </c>
+      <c r="F660" t="n">
+        <v>366.78</v>
+      </c>
+      <c r="G660" t="n">
+        <v>358.51</v>
+      </c>
+      <c r="H660" t="n">
+        <v>360.31</v>
+      </c>
+      <c r="I660" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="661">
+      <c r="A661" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-20 22:05:08+00:00</t>
+        </is>
+      </c>
+      <c r="B661" t="n">
+        <v>377.65</v>
+      </c>
+      <c r="C661" t="n">
+        <v>370.23</v>
+      </c>
+      <c r="D661" t="n">
+        <v>368.99</v>
+      </c>
+      <c r="E661" t="n">
+        <v>368.33</v>
+      </c>
+      <c r="F661" t="n">
+        <v>366.71</v>
+      </c>
+      <c r="G661" t="n">
+        <v>358.68</v>
+      </c>
+      <c r="H661" t="n">
+        <v>360.24</v>
+      </c>
+      <c r="I661" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="662">
+      <c r="A662" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-28 22:05:24+00:00</t>
+        </is>
+      </c>
+      <c r="B662" t="n">
+        <v>377.65</v>
+      </c>
+      <c r="C662" t="n">
+        <v>369.02</v>
+      </c>
+      <c r="D662" t="n">
+        <v>368.44</v>
+      </c>
+      <c r="E662" t="n">
+        <v>367.9</v>
+      </c>
+      <c r="F662" t="n">
+        <v>366.32</v>
+      </c>
+      <c r="G662" t="n">
+        <v>358.52</v>
+      </c>
+      <c r="H662" t="n">
+        <v>359.65</v>
+      </c>
+      <c r="I662" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -22142,7 +22274,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B696"/>
+  <dimension ref="A1:B700"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29105,6 +29237,46 @@
       </c>
       <c r="B696" t="n">
         <v>-0.88</v>
+      </c>
+    </row>
+    <row r="697">
+      <c r="A697" t="inlineStr">
+        <is>
+          <t>2026-07-03 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B697" t="n">
+        <v>0.78</v>
+      </c>
+    </row>
+    <row r="698">
+      <c r="A698" t="inlineStr">
+        <is>
+          <t>2026-07-11 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B698" t="n">
+        <v>-1.23</v>
+      </c>
+    </row>
+    <row r="699">
+      <c r="A699" t="inlineStr">
+        <is>
+          <t>2026-07-20 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B699" t="n">
+        <v>0.35</v>
+      </c>
+    </row>
+    <row r="700">
+      <c r="A700" t="inlineStr">
+        <is>
+          <t>2026-07-28 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B700" t="n">
+        <v>-0.29</v>
       </c>
     </row>
   </sheetData>
@@ -29273,28 +29445,28 @@
         <v>0.0256</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2447341457308741</v>
+        <v>0.2403314664185002</v>
       </c>
       <c r="J2" t="n">
-        <v>657</v>
+        <v>661</v>
       </c>
       <c r="K2" t="n">
-        <v>652</v>
+        <v>656</v>
       </c>
       <c r="L2" t="n">
-        <v>0.01214316676532678</v>
+        <v>0.01186704443014353</v>
       </c>
       <c r="M2" t="n">
-        <v>12.8289870877056</v>
+        <v>12.77151831885133</v>
       </c>
       <c r="N2" t="n">
-        <v>272.0536817104854</v>
+        <v>270.5364746343662</v>
       </c>
       <c r="O2" t="n">
-        <v>16.49404988808041</v>
+        <v>16.447993027551</v>
       </c>
       <c r="P2" t="n">
-        <v>371.5533342193709</v>
+        <v>371.6004677171028</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -29351,28 +29523,28 @@
         <v>0.0379</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1828270820073578</v>
+        <v>0.1789270738000055</v>
       </c>
       <c r="J3" t="n">
-        <v>657</v>
+        <v>661</v>
       </c>
       <c r="K3" t="n">
-        <v>654</v>
+        <v>658</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0386618281333827</v>
+        <v>0.03752461816258401</v>
       </c>
       <c r="M3" t="n">
-        <v>4.671127267792935</v>
+        <v>4.660853036523344</v>
       </c>
       <c r="N3" t="n">
-        <v>46.63441379755098</v>
+        <v>46.41762516178436</v>
       </c>
       <c r="O3" t="n">
-        <v>6.828939434315623</v>
+        <v>6.813048154958569</v>
       </c>
       <c r="P3" t="n">
-        <v>368.5214555420799</v>
+        <v>368.5630840372133</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -29429,28 +29601,28 @@
         <v>0.0366</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3498848281935668</v>
+        <v>0.3426611678228469</v>
       </c>
       <c r="J4" t="n">
-        <v>657</v>
+        <v>661</v>
       </c>
       <c r="K4" t="n">
-        <v>654</v>
+        <v>658</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2029237013274581</v>
+        <v>0.1971081995021996</v>
       </c>
       <c r="M4" t="n">
-        <v>3.728641518044001</v>
+        <v>3.741802655569365</v>
       </c>
       <c r="N4" t="n">
-        <v>26.98043870262778</v>
+        <v>27.03582104649579</v>
       </c>
       <c r="O4" t="n">
-        <v>5.194269794940169</v>
+        <v>5.199598162021348</v>
       </c>
       <c r="P4" t="n">
-        <v>365.6710971381843</v>
+        <v>365.7481907269237</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -29507,28 +29679,28 @@
         <v>0.0425</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2963623640289751</v>
+        <v>0.2887450930405072</v>
       </c>
       <c r="J5" t="n">
-        <v>657</v>
+        <v>661</v>
       </c>
       <c r="K5" t="n">
-        <v>656</v>
+        <v>660</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1669672567865887</v>
+        <v>0.1603379922405836</v>
       </c>
       <c r="M5" t="n">
-        <v>3.678538196722799</v>
+        <v>3.688455955326877</v>
       </c>
       <c r="N5" t="n">
-        <v>24.52486076203425</v>
+        <v>24.61884578717444</v>
       </c>
       <c r="O5" t="n">
-        <v>4.952258147757874</v>
+        <v>4.961738182046131</v>
       </c>
       <c r="P5" t="n">
-        <v>366.7500233401398</v>
+        <v>366.8313729804709</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -29585,28 +29757,28 @@
         <v>0.0516</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2465929274386706</v>
+        <v>0.2367840308321614</v>
       </c>
       <c r="J6" t="n">
-        <v>657</v>
+        <v>661</v>
       </c>
       <c r="K6" t="n">
-        <v>656</v>
+        <v>660</v>
       </c>
       <c r="L6" t="n">
-        <v>0.2067146629772478</v>
+        <v>0.1911005015565391</v>
       </c>
       <c r="M6" t="n">
-        <v>2.816970012376199</v>
+        <v>2.84941696855614</v>
       </c>
       <c r="N6" t="n">
-        <v>13.06017707536718</v>
+        <v>13.38159737922786</v>
       </c>
       <c r="O6" t="n">
-        <v>3.613886699298579</v>
+        <v>3.658086573500942</v>
       </c>
       <c r="P6" t="n">
-        <v>368.5322122691927</v>
+        <v>368.6369678498136</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -29663,28 +29835,28 @@
         <v>0.0478</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.2016464092459582</v>
+        <v>-0.2076808266572838</v>
       </c>
       <c r="J7" t="n">
-        <v>657</v>
+        <v>661</v>
       </c>
       <c r="K7" t="n">
-        <v>656</v>
+        <v>660</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1476992834892146</v>
+        <v>0.155515816075478</v>
       </c>
       <c r="M7" t="n">
-        <v>2.807340298205677</v>
+        <v>2.818761215817198</v>
       </c>
       <c r="N7" t="n">
-        <v>13.13182662039859</v>
+        <v>13.20626978262323</v>
       </c>
       <c r="O7" t="n">
-        <v>3.623786227193677</v>
+        <v>3.634043172916803</v>
       </c>
       <c r="P7" t="n">
-        <v>369.4654805413487</v>
+        <v>369.529928827332</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -29741,28 +29913,28 @@
         <v>0.0439</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.2243255277952201</v>
+        <v>-0.225102934572448</v>
       </c>
       <c r="J8" t="n">
-        <v>657</v>
+        <v>661</v>
       </c>
       <c r="K8" t="n">
-        <v>657</v>
+        <v>661</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1896605288202168</v>
+        <v>0.1927869839324838</v>
       </c>
       <c r="M8" t="n">
-        <v>2.554562454061027</v>
+        <v>2.5430629282084</v>
       </c>
       <c r="N8" t="n">
-        <v>12.01794717583618</v>
+        <v>11.94823583326306</v>
       </c>
       <c r="O8" t="n">
-        <v>3.46669109899284</v>
+        <v>3.45662202638111</v>
       </c>
       <c r="P8" t="n">
-        <v>366.8326326462919</v>
+        <v>366.8409408539443</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -29800,7 +29972,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I658"/>
+  <dimension ref="A1:I662"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -60673,6 +60845,194 @@
         </is>
       </c>
     </row>
+    <row r="659">
+      <c r="A659" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-03 22:11:19+00:00</t>
+        </is>
+      </c>
+      <c r="B659" t="inlineStr">
+        <is>
+          <t>-36.62386128601823,174.7760306592957</t>
+        </is>
+      </c>
+      <c r="C659" t="inlineStr">
+        <is>
+          <t>-36.62389771160491,174.77514594292694</t>
+        </is>
+      </c>
+      <c r="D659" t="inlineStr">
+        <is>
+          <t>-36.624053152296966,174.77428848989808</t>
+        </is>
+      </c>
+      <c r="E659" t="inlineStr">
+        <is>
+          <t>-36.62430700219039,174.77346474425397</t>
+        </is>
+      </c>
+      <c r="F659" t="inlineStr">
+        <is>
+          <t>-36.62463984349561,174.77268658841172</t>
+        </is>
+      </c>
+      <c r="G659" t="inlineStr">
+        <is>
+          <t>-36.6250301544278,174.77193403780095</t>
+        </is>
+      </c>
+      <c r="H659" t="inlineStr">
+        <is>
+          <t>-36.625574918990395,174.77134665552543</t>
+        </is>
+      </c>
+      <c r="I659" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="660">
+      <c r="A660" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-11 22:11:13+00:00</t>
+        </is>
+      </c>
+      <c r="B660" t="inlineStr">
+        <is>
+          <t>-36.623859847343475,174.7760305387553</t>
+        </is>
+      </c>
+      <c r="C660" t="inlineStr">
+        <is>
+          <t>-36.6238899691219,174.77514440876308</t>
+        </is>
+      </c>
+      <c r="D660" t="inlineStr">
+        <is>
+          <t>-36.62403963478089,174.774282936984</t>
+        </is>
+      </c>
+      <c r="E660" t="inlineStr">
+        <is>
+          <t>-36.62429332919961,174.7734564199392</t>
+        </is>
+      </c>
+      <c r="F660" t="inlineStr">
+        <is>
+          <t>-36.62463005468899,174.77267820185114</t>
+        </is>
+      </c>
+      <c r="G660" t="inlineStr">
+        <is>
+          <t>-36.625018476035116,174.7719197490752</t>
+        </is>
+      </c>
+      <c r="H660" t="inlineStr">
+        <is>
+          <t>-36.62557428015374,174.7713457150498</t>
+        </is>
+      </c>
+      <c r="I660" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="661">
+      <c r="A661" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-20 22:05:08+00:00</t>
+        </is>
+      </c>
+      <c r="B661" t="inlineStr">
+        <is>
+          <t>-36.6239177540025,174.77603539051233</t>
+        </is>
+      </c>
+      <c r="C661" t="inlineStr">
+        <is>
+          <t>-36.62388925716943,174.77514426769056</t>
+        </is>
+      </c>
+      <c r="D661" t="inlineStr">
+        <is>
+          <t>-36.624042971383,174.77428430763982</t>
+        </is>
+      </c>
+      <c r="E661" t="inlineStr">
+        <is>
+          <t>-36.62429785989487,174.7734591782917</t>
+        </is>
+      </c>
+      <c r="F661" t="inlineStr">
+        <is>
+          <t>-36.624629535585605,174.77267775710934</t>
+        </is>
+      </c>
+      <c r="G661" t="inlineStr">
+        <is>
+          <t>-36.625019566874066,174.7719210837362</t>
+        </is>
+      </c>
+      <c r="H661" t="inlineStr">
+        <is>
+          <t>-36.62557387362133,174.77134511656527</t>
+        </is>
+      </c>
+      <c r="I661" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="662">
+      <c r="A662" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-28 22:05:24+00:00</t>
+        </is>
+      </c>
+      <c r="B662" t="inlineStr">
+        <is>
+          <t>-36.6239177540025,174.77603539051233</t>
+        </is>
+      </c>
+      <c r="C662" t="inlineStr">
+        <is>
+          <t>-36.623878488888415,174.77514213396904</t>
+        </is>
+      </c>
+      <c r="D662" t="inlineStr">
+        <is>
+          <t>-36.624038265918486,174.7742823746637</t>
+        </is>
+      </c>
+      <c r="E662" t="inlineStr">
+        <is>
+          <t>-36.62429438096815,174.773457060271</t>
+        </is>
+      </c>
+      <c r="F662" t="inlineStr">
+        <is>
+          <t>-36.62462664343805,174.77267527926233</t>
+        </is>
+      </c>
+      <c r="G662" t="inlineStr">
+        <is>
+          <t>-36.625018540202106,174.77191982758467</t>
+        </is>
+      </c>
+      <c r="H662" t="inlineStr">
+        <is>
+          <t>-36.62557044713373,174.77134007219604</t>
+        </is>
+      </c>
+      <c r="I662" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0146/nzd0146.xlsx
+++ b/data/nzd0146/nzd0146.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I662"/>
+  <dimension ref="A1:I666"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22258,6 +22258,138 @@
         <v>359.65</v>
       </c>
       <c r="I662" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="663">
+      <c r="A663" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:11:37+00:00</t>
+        </is>
+      </c>
+      <c r="B663" t="n">
+        <v>379.17</v>
+      </c>
+      <c r="C663" t="n">
+        <v>369.72</v>
+      </c>
+      <c r="D663" t="n">
+        <v>368.95</v>
+      </c>
+      <c r="E663" t="n">
+        <v>368.64</v>
+      </c>
+      <c r="F663" t="n">
+        <v>366.91</v>
+      </c>
+      <c r="G663" t="n">
+        <v>358.98</v>
+      </c>
+      <c r="H663" t="n">
+        <v>359.85</v>
+      </c>
+      <c r="I663" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="664">
+      <c r="A664" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-05 22:05:16+00:00</t>
+        </is>
+      </c>
+      <c r="B664" t="n">
+        <v>379.17</v>
+      </c>
+      <c r="C664" t="n">
+        <v>369.49</v>
+      </c>
+      <c r="D664" t="n">
+        <v>369.05</v>
+      </c>
+      <c r="E664" t="n">
+        <v>368.96</v>
+      </c>
+      <c r="F664" t="n">
+        <v>367.16</v>
+      </c>
+      <c r="G664" t="n">
+        <v>359.43</v>
+      </c>
+      <c r="H664" t="n">
+        <v>360.04</v>
+      </c>
+      <c r="I664" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="665">
+      <c r="A665" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-20 22:11:37+00:00</t>
+        </is>
+      </c>
+      <c r="B665" t="n">
+        <v>379.59</v>
+      </c>
+      <c r="C665" t="n">
+        <v>369.46</v>
+      </c>
+      <c r="D665" t="n">
+        <v>369.15</v>
+      </c>
+      <c r="E665" t="n">
+        <v>369.36</v>
+      </c>
+      <c r="F665" t="n">
+        <v>367.45</v>
+      </c>
+      <c r="G665" t="n">
+        <v>359.2</v>
+      </c>
+      <c r="H665" t="n">
+        <v>360.06</v>
+      </c>
+      <c r="I665" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="666">
+      <c r="A666" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-29 22:05:32+00:00</t>
+        </is>
+      </c>
+      <c r="B666" t="n">
+        <v>378.64</v>
+      </c>
+      <c r="C666" t="n">
+        <v>369</v>
+      </c>
+      <c r="D666" t="n">
+        <v>366.89</v>
+      </c>
+      <c r="E666" t="n">
+        <v>367.63</v>
+      </c>
+      <c r="F666" t="n">
+        <v>366.64</v>
+      </c>
+      <c r="G666" t="n">
+        <v>358.03</v>
+      </c>
+      <c r="H666" t="n">
+        <v>358.71</v>
+      </c>
+      <c r="I666" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -22274,7 +22406,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B700"/>
+  <dimension ref="A1:B705"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29277,6 +29409,56 @@
       </c>
       <c r="B700" t="n">
         <v>-0.29</v>
+      </c>
+    </row>
+    <row r="701">
+      <c r="A701" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B701" t="n">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="702">
+      <c r="A702" t="inlineStr">
+        <is>
+          <t>2026-08-05 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B702" t="n">
+        <v>0.34</v>
+      </c>
+    </row>
+    <row r="703">
+      <c r="A703" t="inlineStr">
+        <is>
+          <t>2026-08-13 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B703" t="n">
+        <v>0.41</v>
+      </c>
+    </row>
+    <row r="704">
+      <c r="A704" t="inlineStr">
+        <is>
+          <t>2026-08-20 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B704" t="n">
+        <v>-0.14</v>
+      </c>
+    </row>
+    <row r="705">
+      <c r="A705" t="inlineStr">
+        <is>
+          <t>2026-08-29 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B705" t="n">
+        <v>0.57</v>
       </c>
     </row>
   </sheetData>
@@ -29445,28 +29627,28 @@
         <v>0.0256</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2403314664185002</v>
+        <v>0.2415927173675141</v>
       </c>
       <c r="J2" t="n">
-        <v>661</v>
+        <v>665</v>
       </c>
       <c r="K2" t="n">
-        <v>656</v>
+        <v>660</v>
       </c>
       <c r="L2" t="n">
-        <v>0.01186704443014353</v>
+        <v>0.01214991493079687</v>
       </c>
       <c r="M2" t="n">
-        <v>12.77151831885133</v>
+        <v>12.70086573045816</v>
       </c>
       <c r="N2" t="n">
-        <v>270.5364746343662</v>
+        <v>268.904256418336</v>
       </c>
       <c r="O2" t="n">
-        <v>16.447993027551</v>
+        <v>16.39830041249202</v>
       </c>
       <c r="P2" t="n">
-        <v>371.6004677171028</v>
+        <v>371.5869089387681</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -29523,28 +29705,28 @@
         <v>0.0379</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1789270738000055</v>
+        <v>0.1742230466110614</v>
       </c>
       <c r="J3" t="n">
-        <v>661</v>
+        <v>665</v>
       </c>
       <c r="K3" t="n">
-        <v>658</v>
+        <v>662</v>
       </c>
       <c r="L3" t="n">
-        <v>0.03752461816258401</v>
+        <v>0.03603893172389006</v>
       </c>
       <c r="M3" t="n">
-        <v>4.660853036523344</v>
+        <v>4.654635132135665</v>
       </c>
       <c r="N3" t="n">
-        <v>46.41762516178436</v>
+        <v>46.23110587472746</v>
       </c>
       <c r="O3" t="n">
-        <v>6.813048154958569</v>
+        <v>6.799345988749761</v>
       </c>
       <c r="P3" t="n">
-        <v>368.5630840372133</v>
+        <v>368.6134605013664</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -29601,28 +29783,28 @@
         <v>0.0366</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3426611678228469</v>
+        <v>0.3349894977462246</v>
       </c>
       <c r="J4" t="n">
-        <v>661</v>
+        <v>665</v>
       </c>
       <c r="K4" t="n">
-        <v>658</v>
+        <v>662</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1971081995021996</v>
+        <v>0.1906510143504031</v>
       </c>
       <c r="M4" t="n">
-        <v>3.741802655569365</v>
+        <v>3.757012323964088</v>
       </c>
       <c r="N4" t="n">
-        <v>27.03582104649579</v>
+        <v>27.12655099485112</v>
       </c>
       <c r="O4" t="n">
-        <v>5.199598162021348</v>
+        <v>5.208315562142055</v>
       </c>
       <c r="P4" t="n">
-        <v>365.7481907269237</v>
+        <v>365.8303535132796</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -29679,28 +29861,28 @@
         <v>0.0425</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2887450930405072</v>
+        <v>0.2816689822603886</v>
       </c>
       <c r="J5" t="n">
-        <v>661</v>
+        <v>665</v>
       </c>
       <c r="K5" t="n">
-        <v>660</v>
+        <v>664</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1603379922405836</v>
+        <v>0.1543835440549779</v>
       </c>
       <c r="M5" t="n">
-        <v>3.688455955326877</v>
+        <v>3.696501520685036</v>
       </c>
       <c r="N5" t="n">
-        <v>24.61884578717444</v>
+        <v>24.68389627460068</v>
       </c>
       <c r="O5" t="n">
-        <v>4.961738182046131</v>
+        <v>4.968289069146508</v>
       </c>
       <c r="P5" t="n">
-        <v>366.8313729804709</v>
+        <v>366.9072039959349</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -29757,28 +29939,28 @@
         <v>0.0516</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2367840308321614</v>
+        <v>0.2273300460408022</v>
       </c>
       <c r="J6" t="n">
-        <v>661</v>
+        <v>665</v>
       </c>
       <c r="K6" t="n">
-        <v>660</v>
+        <v>664</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1911005015565391</v>
+        <v>0.176691865034447</v>
       </c>
       <c r="M6" t="n">
-        <v>2.84941696855614</v>
+        <v>2.880592472126275</v>
       </c>
       <c r="N6" t="n">
-        <v>13.38159737922786</v>
+        <v>13.67800555389544</v>
       </c>
       <c r="O6" t="n">
-        <v>3.658086573500942</v>
+        <v>3.698378773719025</v>
       </c>
       <c r="P6" t="n">
-        <v>368.6369678498136</v>
+        <v>368.738275707001</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -29835,28 +30017,28 @@
         <v>0.0478</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.2076808266572838</v>
+        <v>-0.2136251269153154</v>
       </c>
       <c r="J7" t="n">
-        <v>661</v>
+        <v>665</v>
       </c>
       <c r="K7" t="n">
-        <v>660</v>
+        <v>664</v>
       </c>
       <c r="L7" t="n">
-        <v>0.155515816075478</v>
+        <v>0.1633459407885283</v>
       </c>
       <c r="M7" t="n">
-        <v>2.818761215817198</v>
+        <v>2.831177531270002</v>
       </c>
       <c r="N7" t="n">
-        <v>13.20626978262323</v>
+        <v>13.27716913302161</v>
       </c>
       <c r="O7" t="n">
-        <v>3.634043172916803</v>
+        <v>3.64378500093263</v>
       </c>
       <c r="P7" t="n">
-        <v>369.529928827332</v>
+        <v>369.5936325872821</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -29913,28 +30095,28 @@
         <v>0.0439</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.225102934572448</v>
+        <v>-0.2264099003210309</v>
       </c>
       <c r="J8" t="n">
-        <v>661</v>
+        <v>665</v>
       </c>
       <c r="K8" t="n">
-        <v>661</v>
+        <v>665</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1927869839324838</v>
+        <v>0.1965845808894544</v>
       </c>
       <c r="M8" t="n">
-        <v>2.5430629282084</v>
+        <v>2.534343846043515</v>
       </c>
       <c r="N8" t="n">
-        <v>11.94823583326306</v>
+        <v>11.88537261525603</v>
       </c>
       <c r="O8" t="n">
-        <v>3.45662202638111</v>
+        <v>3.447516876718087</v>
       </c>
       <c r="P8" t="n">
-        <v>366.8409408539443</v>
+        <v>366.8549568501178</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -29972,7 +30154,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I662"/>
+  <dimension ref="A1:I666"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -61033,6 +61215,194 @@
         </is>
       </c>
     </row>
+    <row r="663">
+      <c r="A663" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:11:37+00:00</t>
+        </is>
+      </c>
+      <c r="B663" t="inlineStr">
+        <is>
+          <t>-36.62393142141256,174.77603653564887</t>
+        </is>
+      </c>
+      <c r="C663" t="inlineStr">
+        <is>
+          <t>-36.62388471847248,174.77514336835333</t>
+        </is>
+      </c>
+      <c r="D663" t="inlineStr">
+        <is>
+          <t>-36.6240426291674,174.77428416705973</t>
+        </is>
+      </c>
+      <c r="E663" t="inlineStr">
+        <is>
+          <t>-36.62430036795827,174.77346070523697</t>
+        </is>
+      </c>
+      <c r="F663" t="inlineStr">
+        <is>
+          <t>-36.624631018738164,174.77267902780017</t>
+        </is>
+      </c>
+      <c r="G663" t="inlineStr">
+        <is>
+          <t>-36.62502149188395,174.77192343902044</t>
+        </is>
+      </c>
+      <c r="H663" t="inlineStr">
+        <is>
+          <t>-36.62557160865499,174.77134178215167</t>
+        </is>
+      </c>
+      <c r="I663" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="664">
+      <c r="A664" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-05 22:05:16+00:00</t>
+        </is>
+      </c>
+      <c r="B664" t="inlineStr">
+        <is>
+          <t>-36.62393142141256,174.77603653564887</t>
+        </is>
+      </c>
+      <c r="C664" t="inlineStr">
+        <is>
+          <t>-36.62388267160915,174.77514296276988</t>
+        </is>
+      </c>
+      <c r="D664" t="inlineStr">
+        <is>
+          <t>-36.62404348470639,174.77428451850997</t>
+        </is>
+      </c>
+      <c r="E664" t="inlineStr">
+        <is>
+          <t>-36.62430295692692,174.77346228143864</t>
+        </is>
+      </c>
+      <c r="F664" t="inlineStr">
+        <is>
+          <t>-36.624632872678845,174.7726806161638</t>
+        </is>
+      </c>
+      <c r="G664" t="inlineStr">
+        <is>
+          <t>-36.62502437939869,174.771926971947</t>
+        </is>
+      </c>
+      <c r="H664" t="inlineStr">
+        <is>
+          <t>-36.625572712100144,174.77134340660956</t>
+        </is>
+      </c>
+      <c r="I664" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="665">
+      <c r="A665" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-20 22:11:37+00:00</t>
+        </is>
+      </c>
+      <c r="B665" t="inlineStr">
+        <is>
+          <t>-36.623935197933754,174.77603685206824</t>
+        </is>
+      </c>
+      <c r="C665" t="inlineStr">
+        <is>
+          <t>-36.62388240462697,174.7751429098677</t>
+        </is>
+      </c>
+      <c r="D665" t="inlineStr">
+        <is>
+          <t>-36.62404434024538,174.7742848699602</t>
+        </is>
+      </c>
+      <c r="E665" t="inlineStr">
+        <is>
+          <t>-36.6243061931377,174.77346425169088</t>
+        </is>
+      </c>
+      <c r="F665" t="inlineStr">
+        <is>
+          <t>-36.62463502325002,174.77268245866568</t>
+        </is>
+      </c>
+      <c r="G665" t="inlineStr">
+        <is>
+          <t>-36.62502290355782,174.77192516622895</t>
+        </is>
+      </c>
+      <c r="H665" t="inlineStr">
+        <is>
+          <t>-36.62557282825226,174.77134357760514</t>
+        </is>
+      </c>
+      <c r="I665" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="666">
+      <c r="A666" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-29 22:05:32+00:00</t>
+        </is>
+      </c>
+      <c r="B666" t="inlineStr">
+        <is>
+          <t>-36.623926655802485,174.7760361363578</t>
+        </is>
+      </c>
+      <c r="C666" t="inlineStr">
+        <is>
+          <t>-36.62387831090029,174.77514209870094</t>
+        </is>
+      </c>
+      <c r="D666" t="inlineStr">
+        <is>
+          <t>-36.624025005063736,174.77427692718686</t>
+        </is>
+      </c>
+      <c r="E666" t="inlineStr">
+        <is>
+          <t>-36.624292196525786,174.77345573035115</t>
+        </is>
+      </c>
+      <c r="F666" t="inlineStr">
+        <is>
+          <t>-36.624629016482196,174.77267731236753</t>
+        </is>
+      </c>
+      <c r="G666" t="inlineStr">
+        <is>
+          <t>-36.625015396019144,174.77191598062078</t>
+        </is>
+      </c>
+      <c r="H666" t="inlineStr">
+        <is>
+          <t>-36.62556498798354,174.77133203540535</t>
+        </is>
+      </c>
+      <c r="I666" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0146/nzd0146.xlsx
+++ b/data/nzd0146/nzd0146.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I666"/>
+  <dimension ref="A1:I667"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22390,6 +22390,39 @@
         <v>358.71</v>
       </c>
       <c r="I666" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="667">
+      <c r="A667" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-14 22:06:00+00:00</t>
+        </is>
+      </c>
+      <c r="B667" t="n">
+        <v>381.32</v>
+      </c>
+      <c r="C667" t="n">
+        <v>369.35</v>
+      </c>
+      <c r="D667" t="n">
+        <v>367.61</v>
+      </c>
+      <c r="E667" t="n">
+        <v>368.95</v>
+      </c>
+      <c r="F667" t="n">
+        <v>367.43</v>
+      </c>
+      <c r="G667" t="n">
+        <v>358.96</v>
+      </c>
+      <c r="H667" t="n">
+        <v>359.78</v>
+      </c>
+      <c r="I667" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -22406,7 +22439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B705"/>
+  <dimension ref="A1:B706"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29459,6 +29492,16 @@
       </c>
       <c r="B705" t="n">
         <v>0.57</v>
+      </c>
+    </row>
+    <row r="706">
+      <c r="A706" t="inlineStr">
+        <is>
+          <t>2026-09-14 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B706" t="n">
+        <v>1.16</v>
       </c>
     </row>
   </sheetData>
@@ -29627,28 +29670,28 @@
         <v>0.0256</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2415927173675141</v>
+        <v>0.2425451446829435</v>
       </c>
       <c r="J2" t="n">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="K2" t="n">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="L2" t="n">
-        <v>0.01214991493079687</v>
+        <v>0.01228458108513986</v>
       </c>
       <c r="M2" t="n">
-        <v>12.70086573045816</v>
+        <v>12.6867040157821</v>
       </c>
       <c r="N2" t="n">
-        <v>268.904256418336</v>
+        <v>268.5128011152062</v>
       </c>
       <c r="O2" t="n">
-        <v>16.39830041249202</v>
+        <v>16.38636021559413</v>
       </c>
       <c r="P2" t="n">
-        <v>371.5869089387681</v>
+        <v>371.5766323267631</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -29705,28 +29748,28 @@
         <v>0.0379</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1742230466110614</v>
+        <v>0.1730428314652535</v>
       </c>
       <c r="J3" t="n">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="K3" t="n">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="L3" t="n">
-        <v>0.03603893172389006</v>
+        <v>0.03566673241114293</v>
       </c>
       <c r="M3" t="n">
-        <v>4.654635132135665</v>
+        <v>4.653111404299915</v>
       </c>
       <c r="N3" t="n">
-        <v>46.23110587472746</v>
+        <v>46.1851182345947</v>
       </c>
       <c r="O3" t="n">
-        <v>6.799345988749761</v>
+        <v>6.79596337796156</v>
       </c>
       <c r="P3" t="n">
-        <v>368.6134605013664</v>
+        <v>368.6261435106387</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -29783,28 +29826,28 @@
         <v>0.0366</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3349894977462246</v>
+        <v>0.3328282163546197</v>
       </c>
       <c r="J4" t="n">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="K4" t="n">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1906510143504031</v>
+        <v>0.1887236332730325</v>
       </c>
       <c r="M4" t="n">
-        <v>3.757012323964088</v>
+        <v>3.76201275921574</v>
       </c>
       <c r="N4" t="n">
-        <v>27.12655099485112</v>
+        <v>27.16525708414262</v>
       </c>
       <c r="O4" t="n">
-        <v>5.208315562142055</v>
+        <v>5.212030034846559</v>
       </c>
       <c r="P4" t="n">
-        <v>365.8303535132796</v>
+        <v>365.8535794073272</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -29861,28 +29904,28 @@
         <v>0.0425</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2816689822603886</v>
+        <v>0.2800136136206872</v>
       </c>
       <c r="J5" t="n">
+        <v>666</v>
+      </c>
+      <c r="K5" t="n">
         <v>665</v>
       </c>
-      <c r="K5" t="n">
-        <v>664</v>
-      </c>
       <c r="L5" t="n">
-        <v>0.1543835440549779</v>
+        <v>0.15303978106913</v>
       </c>
       <c r="M5" t="n">
-        <v>3.696501520685036</v>
+        <v>3.69809308978918</v>
       </c>
       <c r="N5" t="n">
-        <v>24.68389627460068</v>
+        <v>24.69331617824231</v>
       </c>
       <c r="O5" t="n">
-        <v>4.968289069146508</v>
+        <v>4.969236981493467</v>
       </c>
       <c r="P5" t="n">
-        <v>366.9072039959349</v>
+        <v>366.9250050128448</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -29939,28 +29982,28 @@
         <v>0.0516</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2273300460408022</v>
+        <v>0.2251148179042152</v>
       </c>
       <c r="J6" t="n">
+        <v>666</v>
+      </c>
+      <c r="K6" t="n">
         <v>665</v>
       </c>
-      <c r="K6" t="n">
-        <v>664</v>
-      </c>
       <c r="L6" t="n">
-        <v>0.176691865034447</v>
+        <v>0.1734678608040633</v>
       </c>
       <c r="M6" t="n">
-        <v>2.880592472126275</v>
+        <v>2.887622682919198</v>
       </c>
       <c r="N6" t="n">
-        <v>13.67800555389544</v>
+        <v>13.74077842421075</v>
       </c>
       <c r="O6" t="n">
-        <v>3.698378773719025</v>
+        <v>3.706855597971244</v>
       </c>
       <c r="P6" t="n">
-        <v>368.738275707001</v>
+        <v>368.7620971764749</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -30017,28 +30060,28 @@
         <v>0.0478</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.2136251269153154</v>
+        <v>-0.2150665869150288</v>
       </c>
       <c r="J7" t="n">
+        <v>666</v>
+      </c>
+      <c r="K7" t="n">
         <v>665</v>
       </c>
-      <c r="K7" t="n">
-        <v>664</v>
-      </c>
       <c r="L7" t="n">
-        <v>0.1633459407885283</v>
+        <v>0.1652871334530506</v>
       </c>
       <c r="M7" t="n">
-        <v>2.831177531270002</v>
+        <v>2.834088464624195</v>
       </c>
       <c r="N7" t="n">
-        <v>13.27716913302161</v>
+        <v>13.2924915867885</v>
       </c>
       <c r="O7" t="n">
-        <v>3.64378500093263</v>
+        <v>3.645886941032114</v>
       </c>
       <c r="P7" t="n">
-        <v>369.5936325872821</v>
+        <v>369.6091333363083</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -30095,28 +30138,28 @@
         <v>0.0439</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.2264099003210309</v>
+        <v>-0.2266923992339934</v>
       </c>
       <c r="J8" t="n">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="K8" t="n">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1965845808894544</v>
+        <v>0.1974906725810507</v>
       </c>
       <c r="M8" t="n">
-        <v>2.534343846043515</v>
+        <v>2.53195069695004</v>
       </c>
       <c r="N8" t="n">
-        <v>11.88537261525603</v>
+        <v>11.86887962347255</v>
       </c>
       <c r="O8" t="n">
-        <v>3.447516876718087</v>
+        <v>3.445124036006911</v>
       </c>
       <c r="P8" t="n">
-        <v>366.8549568501178</v>
+        <v>366.8579956874489</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -30154,7 +30197,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I666"/>
+  <dimension ref="A1:I667"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -61403,6 +61446,53 @@
         </is>
       </c>
     </row>
+    <row r="667">
+      <c r="A667" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-14 22:06:00+00:00</t>
+        </is>
+      </c>
+      <c r="B667" t="inlineStr">
+        <is>
+          <t>-36.62395075360436,174.77603815541522</t>
+        </is>
+      </c>
+      <c r="C667" t="inlineStr">
+        <is>
+          <t>-36.62388142569234,174.77514271589303</t>
+        </is>
+      </c>
+      <c r="D667" t="inlineStr">
+        <is>
+          <t>-36.62403116494469,174.77427945762747</t>
+        </is>
+      </c>
+      <c r="E667" t="inlineStr">
+        <is>
+          <t>-36.62430287602166,174.77346223218234</t>
+        </is>
+      </c>
+      <c r="F667" t="inlineStr">
+        <is>
+          <t>-36.62463487493476,174.7726823315966</t>
+        </is>
+      </c>
+      <c r="G667" t="inlineStr">
+        <is>
+          <t>-36.625021363549955,174.77192328200147</t>
+        </is>
+      </c>
+      <c r="H667" t="inlineStr">
+        <is>
+          <t>-36.62557120212254,174.77134118366718</t>
+        </is>
+      </c>
+      <c r="I667" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
